--- a/Matched_DMAs_Updated.xlsx
+++ b/Matched_DMAs_Updated.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dhoy/Documents/Scripts/Script_Updater/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{69FEFC6E-C108-EE4E-AC25-F65B2C89AE39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9954970E-F59C-8D43-BC69-EA75B08979B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-80" yWindow="780" windowWidth="29400" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="29400" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="REF" sheetId="1" r:id="rId1"/>
@@ -1016,6 +1016,9 @@
     <t>DMA ID</t>
   </si>
   <si>
+    <t>Search DMA</t>
+  </si>
+  <si>
     <t>Population</t>
   </si>
   <si>
@@ -1587,9 +1590,6 @@
   </si>
   <si>
     <t>Alpena, MI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Search DMA</t>
   </si>
 </sst>
 </file>
@@ -1985,13 +1985,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>517</v>
+        <v>326</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>325</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -2002,7 +2002,7 @@
         <v>208</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D2">
         <v>662</v>
@@ -2019,7 +2019,7 @@
         <v>209</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D3">
         <v>532</v>
@@ -2053,7 +2053,7 @@
         <v>211</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D5">
         <v>790</v>
@@ -2087,7 +2087,7 @@
         <v>7</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D7">
         <v>634</v>
@@ -2104,7 +2104,7 @@
         <v>8</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D8">
         <v>524</v>
@@ -2121,7 +2121,7 @@
         <v>213</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D9">
         <v>520</v>
@@ -2138,7 +2138,7 @@
         <v>10</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D10">
         <v>635</v>
@@ -2155,7 +2155,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D11">
         <v>800</v>
@@ -2172,7 +2172,7 @@
         <v>12</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D12">
         <v>512</v>
@@ -2189,7 +2189,7 @@
         <v>13</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D13">
         <v>537</v>
@@ -2206,7 +2206,7 @@
         <v>14</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D14">
         <v>716</v>
@@ -2223,7 +2223,7 @@
         <v>214</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D15">
         <v>692</v>
@@ -2240,7 +2240,7 @@
         <v>215</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D16">
         <v>559</v>
@@ -2274,7 +2274,7 @@
         <v>18</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D18">
         <v>756</v>
@@ -2291,7 +2291,7 @@
         <v>217</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D19">
         <v>746</v>
@@ -2308,7 +2308,7 @@
         <v>20</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D20">
         <v>502</v>
@@ -2325,7 +2325,7 @@
         <v>21</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D21">
         <v>757</v>
@@ -2342,7 +2342,7 @@
         <v>22</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D22">
         <v>736</v>
@@ -2359,7 +2359,7 @@
         <v>23</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D23">
         <v>514</v>
@@ -2376,7 +2376,7 @@
         <v>218</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D24">
         <v>523</v>
@@ -2393,7 +2393,7 @@
         <v>219</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D25">
         <v>754</v>
@@ -2410,7 +2410,7 @@
         <v>220</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D26">
         <v>767</v>
@@ -2427,7 +2427,7 @@
         <v>221</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D27">
         <v>637</v>
@@ -2444,7 +2444,7 @@
         <v>222</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D28">
         <v>648</v>
@@ -2461,7 +2461,7 @@
         <v>223</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D29">
         <v>564</v>
@@ -2495,7 +2495,7 @@
         <v>31</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D31">
         <v>517</v>
@@ -2512,7 +2512,7 @@
         <v>32</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D32">
         <v>584</v>
@@ -2529,7 +2529,7 @@
         <v>33</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D33">
         <v>575</v>
@@ -2546,7 +2546,7 @@
         <v>34</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D34">
         <v>602</v>
@@ -2563,7 +2563,7 @@
         <v>225</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D35">
         <v>868</v>
@@ -2580,7 +2580,7 @@
         <v>36</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D36">
         <v>515</v>
@@ -2597,7 +2597,7 @@
         <v>226</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D37">
         <v>598</v>
@@ -2614,7 +2614,7 @@
         <v>227</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D38">
         <v>752</v>
@@ -2631,7 +2631,7 @@
         <v>228</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D39">
         <v>604</v>
@@ -2665,7 +2665,7 @@
         <v>230</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D41">
         <v>673</v>
@@ -2699,7 +2699,7 @@
         <v>43</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D43">
         <v>600</v>
@@ -2716,7 +2716,7 @@
         <v>232</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D44">
         <v>623</v>
@@ -2733,7 +2733,7 @@
         <v>233</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D45">
         <v>682</v>
@@ -2750,7 +2750,7 @@
         <v>46</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D46">
         <v>542</v>
@@ -2767,7 +2767,7 @@
         <v>47</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D47">
         <v>751</v>
@@ -2784,7 +2784,7 @@
         <v>234</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D48">
         <v>679</v>
@@ -2801,7 +2801,7 @@
         <v>49</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D49">
         <v>505</v>
@@ -2818,7 +2818,7 @@
         <v>50</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D50">
         <v>606</v>
@@ -2835,7 +2835,7 @@
         <v>235</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D51">
         <v>676</v>
@@ -2852,7 +2852,7 @@
         <v>52</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D52">
         <v>516</v>
@@ -2869,7 +2869,7 @@
         <v>53</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D53">
         <v>801</v>
@@ -2886,7 +2886,7 @@
         <v>54</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D54">
         <v>802</v>
@@ -2903,7 +2903,7 @@
         <v>55</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D55">
         <v>649</v>
@@ -2920,7 +2920,7 @@
         <v>236</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D56">
         <v>724</v>
@@ -2937,7 +2937,7 @@
         <v>237</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D57">
         <v>513</v>
@@ -2954,7 +2954,7 @@
         <v>238</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D58">
         <v>866</v>
@@ -2971,7 +2971,7 @@
         <v>239</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D59">
         <v>509</v>
@@ -2988,7 +2988,7 @@
         <v>240</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D60">
         <v>571</v>
@@ -3005,7 +3005,7 @@
         <v>61</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D61">
         <v>592</v>
@@ -3022,7 +3022,7 @@
         <v>241</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D62">
         <v>773</v>
@@ -3039,7 +3039,7 @@
         <v>63</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D63">
         <v>755</v>
@@ -3056,7 +3056,7 @@
         <v>242</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D64">
         <v>658</v>
@@ -3073,7 +3073,7 @@
         <v>243</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D65">
         <v>567</v>
@@ -3090,7 +3090,7 @@
         <v>244</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D66">
         <v>647</v>
@@ -3107,7 +3107,7 @@
         <v>245</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D67">
         <v>636</v>
@@ -3124,7 +3124,7 @@
         <v>68</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D68">
         <v>569</v>
@@ -3141,7 +3141,7 @@
         <v>246</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D69">
         <v>533</v>
@@ -3158,7 +3158,7 @@
         <v>70</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D70">
         <v>766</v>
@@ -3175,7 +3175,7 @@
         <v>71</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D71">
         <v>618</v>
@@ -3192,7 +3192,7 @@
         <v>247</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D72">
         <v>691</v>
@@ -3209,7 +3209,7 @@
         <v>248</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D73">
         <v>758</v>
@@ -3226,7 +3226,7 @@
         <v>74</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D74">
         <v>527</v>
@@ -3277,7 +3277,7 @@
         <v>251</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D77">
         <v>561</v>
@@ -3294,7 +3294,7 @@
         <v>252</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D78">
         <v>574</v>
@@ -3311,7 +3311,7 @@
         <v>79</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D79">
         <v>734</v>
@@ -3328,7 +3328,7 @@
         <v>253</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D80">
         <v>603</v>
@@ -3345,7 +3345,7 @@
         <v>81</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D81">
         <v>616</v>
@@ -3362,7 +3362,7 @@
         <v>82</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D82">
         <v>557</v>
@@ -3379,7 +3379,7 @@
         <v>254</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D83">
         <v>702</v>
@@ -3430,7 +3430,7 @@
         <v>86</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D86">
         <v>643</v>
@@ -3447,7 +3447,7 @@
         <v>87</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D87">
         <v>551</v>
@@ -3464,7 +3464,7 @@
         <v>88</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D88">
         <v>749</v>
@@ -3481,7 +3481,7 @@
         <v>89</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D89">
         <v>839</v>
@@ -3498,7 +3498,7 @@
         <v>257</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D90">
         <v>710</v>
@@ -3515,7 +3515,7 @@
         <v>91</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D91">
         <v>541</v>
@@ -3532,7 +3532,7 @@
         <v>92</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D92">
         <v>558</v>
@@ -3549,7 +3549,7 @@
         <v>258</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D93">
         <v>722</v>
@@ -3566,7 +3566,7 @@
         <v>259</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D94">
         <v>693</v>
@@ -3583,7 +3583,7 @@
         <v>95</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D95">
         <v>803</v>
@@ -3600,7 +3600,7 @@
         <v>96</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D96">
         <v>529</v>
@@ -3617,7 +3617,7 @@
         <v>97</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D97">
         <v>651</v>
@@ -3634,7 +3634,7 @@
         <v>98</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D98">
         <v>503</v>
@@ -3651,7 +3651,7 @@
         <v>99</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D99">
         <v>669</v>
@@ -3668,7 +3668,7 @@
         <v>100</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D100">
         <v>737</v>
@@ -3685,7 +3685,7 @@
         <v>101</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D101">
         <v>553</v>
@@ -3702,7 +3702,7 @@
         <v>260</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D102">
         <v>813</v>
@@ -3719,7 +3719,7 @@
         <v>103</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D103">
         <v>640</v>
@@ -3736,7 +3736,7 @@
         <v>104</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D104">
         <v>711</v>
@@ -3753,7 +3753,7 @@
         <v>261</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D105">
         <v>528</v>
@@ -3770,7 +3770,7 @@
         <v>106</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D106">
         <v>617</v>
@@ -3787,7 +3787,7 @@
         <v>262</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D107">
         <v>613</v>
@@ -3804,7 +3804,7 @@
         <v>108</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D108">
         <v>762</v>
@@ -3821,7 +3821,7 @@
         <v>263</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D109">
         <v>686</v>
@@ -3838,7 +3838,7 @@
         <v>264</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D110">
         <v>628</v>
@@ -3855,7 +3855,7 @@
         <v>265</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D111">
         <v>828</v>
@@ -3872,7 +3872,7 @@
         <v>266</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D112">
         <v>698</v>
@@ -3889,7 +3889,7 @@
         <v>113</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D113">
         <v>659</v>
@@ -3906,7 +3906,7 @@
         <v>114</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D114">
         <v>622</v>
@@ -3923,7 +3923,7 @@
         <v>115</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D115">
         <v>501</v>
@@ -3940,7 +3940,7 @@
         <v>267</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D116">
         <v>544</v>
@@ -3957,7 +3957,7 @@
         <v>117</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D117">
         <v>740</v>
@@ -3974,7 +3974,7 @@
         <v>268</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D118">
         <v>633</v>
@@ -3991,7 +3991,7 @@
         <v>119</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D119">
         <v>650</v>
@@ -4008,7 +4008,7 @@
         <v>120</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D120">
         <v>652</v>
@@ -4025,7 +4025,7 @@
         <v>269</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D121">
         <v>534</v>
@@ -4042,7 +4042,7 @@
         <v>270</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D122">
         <v>631</v>
@@ -4059,7 +4059,7 @@
         <v>123</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D123">
         <v>804</v>
@@ -4076,7 +4076,7 @@
         <v>124</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D124">
         <v>656</v>
@@ -4093,7 +4093,7 @@
         <v>125</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D125">
         <v>597</v>
@@ -4110,7 +4110,7 @@
         <v>271</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D126">
         <v>675</v>
@@ -4127,7 +4127,7 @@
         <v>127</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D127">
         <v>504</v>
@@ -4144,7 +4144,7 @@
         <v>128</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D128">
         <v>508</v>
@@ -4161,7 +4161,7 @@
         <v>272</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D129">
         <v>500</v>
@@ -4195,7 +4195,7 @@
         <v>131</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D131">
         <v>552</v>
@@ -4212,7 +4212,7 @@
         <v>274</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D132">
         <v>521</v>
@@ -4229,7 +4229,7 @@
         <v>275</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D133">
         <v>717</v>
@@ -4246,7 +4246,7 @@
         <v>276</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D134">
         <v>560</v>
@@ -4263,7 +4263,7 @@
         <v>135</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D135">
         <v>764</v>
@@ -4280,7 +4280,7 @@
         <v>136</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D136">
         <v>811</v>
@@ -4297,7 +4297,7 @@
         <v>277</v>
       </c>
       <c r="C137" s="6" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D137">
         <v>556</v>
@@ -4314,7 +4314,7 @@
         <v>278</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D138">
         <v>573</v>
@@ -4331,7 +4331,7 @@
         <v>279</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D139">
         <v>611</v>
@@ -4365,7 +4365,7 @@
         <v>141</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D141">
         <v>610</v>
@@ -4382,7 +4382,7 @@
         <v>143</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D142">
         <v>576</v>
@@ -4399,7 +4399,7 @@
         <v>144</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D143">
         <v>770</v>
@@ -4416,7 +4416,7 @@
         <v>145</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D144">
         <v>661</v>
@@ -4433,7 +4433,7 @@
         <v>146</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D145">
         <v>641</v>
@@ -4450,7 +4450,7 @@
         <v>147</v>
       </c>
       <c r="C146" s="6" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D146">
         <v>825</v>
@@ -4467,7 +4467,7 @@
         <v>281</v>
       </c>
       <c r="C147" s="6" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D147">
         <v>807</v>
@@ -4484,7 +4484,7 @@
         <v>149</v>
       </c>
       <c r="C148" s="6" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D148">
         <v>507</v>
@@ -4501,7 +4501,7 @@
         <v>282</v>
       </c>
       <c r="C149" s="6" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D149">
         <v>819</v>
@@ -4518,7 +4518,7 @@
         <v>283</v>
       </c>
       <c r="C150" s="6" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D150">
         <v>657</v>
@@ -4535,7 +4535,7 @@
         <v>284</v>
       </c>
       <c r="C151" s="6" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D151">
         <v>612</v>
@@ -4552,7 +4552,7 @@
         <v>153</v>
       </c>
       <c r="C152" s="6" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D152">
         <v>624</v>
@@ -4569,7 +4569,7 @@
         <v>285</v>
       </c>
       <c r="C153" s="6" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D153">
         <v>725</v>
@@ -4586,7 +4586,7 @@
         <v>286</v>
       </c>
       <c r="C154" s="6" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D154">
         <v>588</v>
@@ -4603,7 +4603,7 @@
         <v>156</v>
       </c>
       <c r="C155" s="6" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D155">
         <v>881</v>
@@ -4620,7 +4620,7 @@
         <v>287</v>
       </c>
       <c r="C156" s="6" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D156">
         <v>543</v>
@@ -4654,7 +4654,7 @@
         <v>289</v>
       </c>
       <c r="C158" s="6" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D158">
         <v>638</v>
@@ -4671,7 +4671,7 @@
         <v>290</v>
       </c>
       <c r="C159" s="6" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D159">
         <v>609</v>
@@ -4688,7 +4688,7 @@
         <v>161</v>
       </c>
       <c r="C160" s="6" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D160">
         <v>555</v>
@@ -4705,7 +4705,7 @@
         <v>291</v>
       </c>
       <c r="C161" s="6" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D161">
         <v>530</v>
@@ -4722,7 +4722,7 @@
         <v>292</v>
       </c>
       <c r="C162" s="6" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D162">
         <v>539</v>
@@ -4756,7 +4756,7 @@
         <v>165</v>
       </c>
       <c r="C164" s="6" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D164">
         <v>547</v>
@@ -4773,7 +4773,7 @@
         <v>166</v>
       </c>
       <c r="C165" s="6" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D165">
         <v>605</v>
@@ -4790,7 +4790,7 @@
         <v>293</v>
       </c>
       <c r="C166" s="6" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D166">
         <v>540</v>
@@ -4824,7 +4824,7 @@
         <v>169</v>
       </c>
       <c r="C168" s="6" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D168">
         <v>671</v>
@@ -4841,7 +4841,7 @@
         <v>170</v>
       </c>
       <c r="C169" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D169">
         <v>760</v>
@@ -4858,7 +4858,7 @@
         <v>295</v>
       </c>
       <c r="C170" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D170">
         <v>709</v>
@@ -4875,7 +4875,7 @@
         <v>172</v>
       </c>
       <c r="C171" s="6" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D171">
         <v>526</v>
@@ -4892,7 +4892,7 @@
         <v>173</v>
       </c>
       <c r="C172" s="6" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D172">
         <v>626</v>
@@ -4909,7 +4909,7 @@
         <v>296</v>
       </c>
       <c r="C173" s="6" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D173">
         <v>625</v>
@@ -4926,7 +4926,7 @@
         <v>297</v>
       </c>
       <c r="C174" s="6" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D174">
         <v>511</v>
@@ -4943,7 +4943,7 @@
         <v>298</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D175">
         <v>549</v>
@@ -4960,7 +4960,7 @@
         <v>177</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D176">
         <v>705</v>
@@ -4977,7 +4977,7 @@
         <v>299</v>
       </c>
       <c r="C177" s="6" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D177">
         <v>548</v>
@@ -4994,7 +4994,7 @@
         <v>300</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D178">
         <v>554</v>
@@ -5011,7 +5011,7 @@
         <v>301</v>
       </c>
       <c r="C179" s="6" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D179">
         <v>627</v>
@@ -5028,7 +5028,7 @@
         <v>302</v>
       </c>
       <c r="C180" s="6" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D180">
         <v>678</v>
@@ -5045,7 +5045,7 @@
         <v>303</v>
       </c>
       <c r="C181" s="6" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D181">
         <v>577</v>
@@ -5062,7 +5062,7 @@
         <v>183</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D182">
         <v>550</v>
@@ -5079,7 +5079,7 @@
         <v>184</v>
       </c>
       <c r="C183" s="6" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D183">
         <v>536</v>
@@ -5096,7 +5096,7 @@
         <v>304</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D184">
         <v>771</v>
@@ -5113,7 +5113,7 @@
         <v>186</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D185">
         <v>596</v>
@@ -5130,7 +5130,7 @@
         <v>187</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D186">
         <v>583</v>
@@ -5147,7 +5147,7 @@
         <v>305</v>
       </c>
       <c r="C187" s="6" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D187" s="2">
         <v>862</v>
@@ -5164,7 +5164,7 @@
         <v>306</v>
       </c>
       <c r="C188" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D188" s="4">
         <v>630</v>
@@ -5181,7 +5181,7 @@
         <v>307</v>
       </c>
       <c r="C189" s="6" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D189" s="2">
         <v>506</v>
@@ -5198,7 +5198,7 @@
         <v>308</v>
       </c>
       <c r="C190" s="6" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D190" s="2">
         <v>753</v>
@@ -5215,7 +5215,7 @@
         <v>309</v>
       </c>
       <c r="C191" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D191" s="2">
         <v>510</v>
@@ -5232,7 +5232,7 @@
         <v>310</v>
       </c>
       <c r="C192" s="6" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D192" s="2">
         <v>566</v>
@@ -5249,7 +5249,7 @@
         <v>311</v>
       </c>
       <c r="C193" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D193" s="2">
         <v>518</v>
@@ -5266,7 +5266,7 @@
         <v>312</v>
       </c>
       <c r="C194" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D194" s="2">
         <v>670</v>
@@ -5283,7 +5283,7 @@
         <v>313</v>
       </c>
       <c r="C195" s="6" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D195" s="2">
         <v>789</v>
@@ -5300,7 +5300,7 @@
         <v>314</v>
       </c>
       <c r="C196" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D196" s="2">
         <v>563</v>
@@ -5317,7 +5317,7 @@
         <v>315</v>
       </c>
       <c r="C197" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D197" s="2">
         <v>765</v>
@@ -5334,7 +5334,7 @@
         <v>316</v>
       </c>
       <c r="C198" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D198" s="2">
         <v>545</v>
@@ -5351,7 +5351,7 @@
         <v>317</v>
       </c>
       <c r="C199" s="6" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D199" s="2">
         <v>632</v>
@@ -5368,7 +5368,7 @@
         <v>318</v>
       </c>
       <c r="C200" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D200" s="2">
         <v>570</v>
@@ -5385,7 +5385,7 @@
         <v>319</v>
       </c>
       <c r="C201" s="6" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D201" s="2">
         <v>855</v>
@@ -5402,7 +5402,7 @@
         <v>320</v>
       </c>
       <c r="C202" s="6" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D202" s="2">
         <v>522</v>
@@ -5419,7 +5419,7 @@
         <v>321</v>
       </c>
       <c r="C203" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D203" s="2">
         <v>565</v>
@@ -5436,7 +5436,7 @@
         <v>322</v>
       </c>
       <c r="C204" s="6" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D204">
         <v>810</v>
@@ -5453,7 +5453,7 @@
         <v>323</v>
       </c>
       <c r="C205" s="6" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D205" s="2">
         <v>687</v>
@@ -5470,7 +5470,7 @@
         <v>324</v>
       </c>
       <c r="C206" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D206" s="2">
         <v>759</v>
